--- a/experiments/results/resnet34/CIFAR-10/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -911,6 +911,55 @@
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.0,type=avg</t>
         </is>
       </c>
     </row>
